--- a/Recipe sheet workbook format.xlsx
+++ b/Recipe sheet workbook format.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Documents\GitHub\reactor_pressure_data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F60CE687-9FC9-4064-AE12-A2BF36EB03C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5457DB9-019A-44E2-AFA8-9D8587659762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{539505D8-28CE-4AF5-B1B8-D9A0288D63DA}"/>
   </bookViews>
@@ -33,10 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
-  <si>
-    <t>User/File Name Info</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t>Info</t>
   </si>
@@ -50,15 +47,6 @@
     <t>DID</t>
   </si>
   <si>
-    <t>SID</t>
-  </si>
-  <si>
-    <t>EID</t>
-  </si>
-  <si>
-    <t>PID</t>
-  </si>
-  <si>
     <t>Valve/precursor</t>
   </si>
   <si>
@@ -92,22 +80,86 @@
     <t>Purge</t>
   </si>
   <si>
-    <t>Jay&amp;TDIC&amp;DAMDPA&amp;HeatSatCurve_1</t>
-  </si>
-  <si>
     <t>In order for this workbook to function as a recipe sheet, this worksheet must be the first sheet of the book and columns A:I must remain strictly dedicated to the recipe sheet information</t>
   </si>
   <si>
     <t>Notes</t>
+  </si>
+  <si>
+    <t>Chamber</t>
+  </si>
+  <si>
+    <t>TDIC</t>
+  </si>
+  <si>
+    <t>DAMDPA</t>
+  </si>
+  <si>
+    <t>MeI</t>
+  </si>
+  <si>
+    <t>Deposit an initial layer of TDIC &amp; DAMDPA. Precursors are heated</t>
+  </si>
+  <si>
+    <t>nan</t>
+  </si>
+  <si>
+    <t>LeakRate</t>
+  </si>
+  <si>
+    <t>SiO2 layer</t>
+  </si>
+  <si>
+    <t>Thickness # 2 vs. Time</t>
+  </si>
+  <si>
+    <t>Time (min.)</t>
+  </si>
+  <si>
+    <t>Thickness # 2</t>
+  </si>
+  <si>
+    <t>Process (1)</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Jay</t>
+  </si>
+  <si>
+    <t>GV</t>
+  </si>
+  <si>
+    <t>Process time:</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>Start time</t>
+  </si>
+  <si>
+    <t>End time</t>
+  </si>
+  <si>
+    <t>Existing layer</t>
+  </si>
+  <si>
+    <t>Thickness</t>
+  </si>
+  <si>
+    <t>SiO2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm\ AM/PM"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="mm/dd/yy\ h:mm\ AM/PM"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -426,7 +478,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -546,37 +598,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -635,22 +656,19 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -707,6 +725,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1026,146 +1048,854 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{456AF080-381C-4412-8C71-8F493E8A8FF3}">
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="6"/>
-    <col min="2" max="2" width="9.140625" style="10" customWidth="1"/>
-    <col min="3" max="9" width="9.140625" style="10"/>
-    <col min="10" max="10" width="9.140625" style="7"/>
+    <col min="1" max="1" width="18.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="4"/>
+    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.28515625" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3">
+        <f>SUM(C12:I23)*A12</f>
+        <v>61620</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q3">
+        <v>18.53</v>
+      </c>
+      <c r="R3" s="5"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" s="7">
+        <v>46239</v>
+      </c>
+      <c r="N4" s="5"/>
+      <c r="R4" s="5"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>137</v>
+      </c>
+      <c r="L5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5" s="7">
+        <f ca="1">NOW()+M3/3600/24</f>
+        <v>46239.536869560179</v>
+      </c>
+      <c r="P5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>12</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="M6" t="s">
+        <v>37</v>
+      </c>
+      <c r="P6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="5"/>
-    </row>
-    <row r="2" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="F7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M7">
+        <v>18.53</v>
+      </c>
+      <c r="P7" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>100</v>
+      </c>
+      <c r="C8">
+        <v>60</v>
+      </c>
+      <c r="D8">
+        <v>50</v>
+      </c>
+      <c r="E8">
+        <v>40</v>
+      </c>
+      <c r="F8">
+        <v>25</v>
+      </c>
+      <c r="G8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M8">
+        <v>4.93</v>
+      </c>
+      <c r="P8">
+        <v>2.3370920000000002</v>
+      </c>
+      <c r="Q8">
+        <v>0.44405899999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="M9" s="2"/>
+      <c r="P9">
+        <v>28.316841</v>
+      </c>
+      <c r="Q9">
+        <v>4.9262079999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M10" s="1"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
         <v>1</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>15</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
         <v>20</v>
       </c>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>60</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <v>8</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>60</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>12</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>60</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <v>7</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>15</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>20</v>
+      </c>
+      <c r="B16">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="C16">
+        <v>4</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>60</v>
+      </c>
+      <c r="G16">
+        <v>300</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>60</v>
+      </c>
+      <c r="G17">
+        <v>300</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>12</v>
+      </c>
+      <c r="C18">
+        <v>4</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>60</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B19">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>15</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>5</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>60</v>
+      </c>
+      <c r="G20">
+        <v>300</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B21">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="C21">
+        <v>4</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>60</v>
+      </c>
+      <c r="G21">
+        <v>300</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <v>12</v>
+      </c>
+      <c r="C22">
+        <v>4</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>60</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="M12" s="2"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="10" t="s">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <v>7</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
         <v>15</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="M13" s="1"/>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100858A5F568ED10E40B22155731D9FBF2A" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4d0e3cf096ece22b69ad0631913f9737">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="60d5a4fa-dfb8-4032-a39f-c398b36dd0e4" xmlns:ns3="8524c750-d52a-4243-9720-728bc70efb7c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="77d17406065d2f34dfa167ed779718a4" ns2:_="" ns3:_="">
+    <xsd:import namespace="60d5a4fa-dfb8-4032-a39f-c398b36dd0e4"/>
+    <xsd:import namespace="8524c750-d52a-4243-9720-728bc70efb7c"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="60d5a4fa-dfb8-4032-a39f-c398b36dd0e4" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="e20148b9-20a4-48a0-acba-ba52d68a37a3" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="17" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8524c750-d52a-4243-9720-728bc70efb7c" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{92542ec2-c00a-4af7-95b1-462edd8f4181}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="8524c750-d52a-4243-9720-728bc70efb7c">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8524c750-d52a-4243-9720-728bc70efb7c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="60d5a4fa-dfb8-4032-a39f-c398b36dd0e4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{010FBDC9-D7DE-46DA-94AB-5E18B7FC2084}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E4B112F-BBCA-4777-BDA8-B098500067E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="60d5a4fa-dfb8-4032-a39f-c398b36dd0e4"/>
+    <ds:schemaRef ds:uri="8524c750-d52a-4243-9720-728bc70efb7c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{105801AB-C7A2-453F-BAA2-8972793E6FDA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8524c750-d52a-4243-9720-728bc70efb7c"/>
+    <ds:schemaRef ds:uri="60d5a4fa-dfb8-4032-a39f-c398b36dd0e4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{f6b6dd5b-f02f-441a-99a0-162ac5060bd2}" enabled="0" method="" siteId="{f6b6dd5b-f02f-441a-99a0-162ac5060bd2}" removed="1"/>
+</clbl:labelList>
 </file>